--- a/samples/Template_Pengajuan_Resmi_Yayasan.xlsx
+++ b/samples/Template_Pengajuan_Resmi_Yayasan.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="38">
   <si>
     <t>YAYASAN PENDIDIKAN ISLAM PONDOK PESANTREN AL-QUR'ANIYYAH</t>
   </si>
@@ -28,7 +28,7 @@
     <t>Nama Kegiatan:</t>
   </si>
   <si>
-    <t>Ujian Semester / Kegiatan Tahunan</t>
+    <t>STS Semester Ganjil / Kegiatan Tahunan</t>
   </si>
   <si>
     <t>Tahun Anggaran:</t>
@@ -49,10 +49,22 @@
     <t>Harga Satuan</t>
   </si>
   <si>
-    <t>Volume</t>
-  </si>
-  <si>
-    <t>Satuan</t>
+    <t>Volume 1</t>
+  </si>
+  <si>
+    <t>Satuan 1</t>
+  </si>
+  <si>
+    <t>Volume 2</t>
+  </si>
+  <si>
+    <t>Satuan 2</t>
+  </si>
+  <si>
+    <t>Volume 3</t>
+  </si>
+  <si>
+    <t>Satuan 3</t>
   </si>
   <si>
     <t>Jumlah</t>
@@ -64,22 +76,40 @@
     <t>ATK</t>
   </si>
   <si>
-    <t>Kertas HVS A4 75 gram</t>
+    <t>Penggandaan LJK (Lembar Jawaban Komputer)</t>
+  </si>
+  <si>
+    <t>MP</t>
+  </si>
+  <si>
+    <t>Siswa</t>
+  </si>
+  <si>
+    <t>Lembar</t>
+  </si>
+  <si>
+    <t>16 MP × 237 Siswa × 2 Lembar</t>
+  </si>
+  <si>
+    <t>Upah</t>
+  </si>
+  <si>
+    <t>Pembuatan Soal Ujian</t>
+  </si>
+  <si>
+    <t>Kelas</t>
+  </si>
+  <si>
+    <t>16 MP × 3 Kelas</t>
+  </si>
+  <si>
+    <t>Kertas HVS F4 70 gram</t>
   </si>
   <si>
     <t>Rim</t>
   </si>
   <si>
-    <t>Administrasi sekolah</t>
-  </si>
-  <si>
-    <t>Tinta Printer Epson Original</t>
-  </si>
-  <si>
-    <t>Botol</t>
-  </si>
-  <si>
-    <t>Printer kantor</t>
+    <t>Kebutuhan cetak ujian</t>
   </si>
   <si>
     <t>Konsumsi</t>
@@ -91,19 +121,7 @@
     <t>Kotak</t>
   </si>
   <si>
-    <t>Persiapan ujian</t>
-  </si>
-  <si>
-    <t>Honorarium</t>
-  </si>
-  <si>
-    <t>Honor Pengawas Ujian per Sesi</t>
-  </si>
-  <si>
-    <t>Orang/Sesi</t>
-  </si>
-  <si>
-    <t>Pengawas ujian</t>
+    <t>Persiapan panitia</t>
   </si>
   <si>
     <t>TOTAL USULAN ANGGARAN</t>
@@ -602,21 +620,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:I14"/>
+  <dimension ref="B2:M14"/>
   <sheetFormatPr defaultRowHeight="22" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="6" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="4" max="4" width="38" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="30" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
+    <col min="12" max="12" width="18" customWidth="1"/>
+    <col min="13" max="13" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -627,8 +649,12 @@
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
@@ -639,6 +665,10 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
@@ -664,7 +694,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" ht="26" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="9" ht="26" customHeight="1" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>8</v>
       </c>
@@ -683,137 +713,185 @@
       <c r="G9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="H9" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" ht="22" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B10" s="7">
         <v>1</v>
       </c>
       <c r="C10" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="9">
+        <v>150</v>
+      </c>
+      <c r="F10" s="7">
         <v>16</v>
       </c>
-      <c r="D10" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="9">
-        <v>75000</v>
-      </c>
-      <c r="F10" s="7">
-        <v>10</v>
-      </c>
       <c r="G10" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="H10" s="9">
-        <v>750000</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="H10" s="7">
+        <v>237</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" s="7">
+        <v>2</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="9">
+        <f>E10*IF(F10&gt;0,F10,1)*IF(H10&gt;0,H10,1)*IF(J10&gt;0,J10,1)</f>
+        <v>1137600</v>
+      </c>
+      <c r="M10" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B11" s="7">
         <v>2</v>
       </c>
       <c r="C11" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="9">
+        <v>35000</v>
+      </c>
+      <c r="F11" s="7">
         <v>16</v>
       </c>
-      <c r="D11" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="9">
-        <v>100000</v>
-      </c>
-      <c r="F11" s="7">
-        <v>4</v>
-      </c>
       <c r="G11" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="H11" s="9">
-        <v>400000</v>
-      </c>
-      <c r="I11" s="8" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="12" ht="22" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="H11" s="7">
+        <v>3</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="9">
+        <f>E11*IF(F11&gt;0,F11,1)*IF(H11&gt;0,H11,1)*IF(J11&gt;0,J11,1)</f>
+        <v>1680000</v>
+      </c>
+      <c r="M11" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B12" s="7">
         <v>3</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E12" s="9">
-        <v>18000</v>
+        <v>57000</v>
       </c>
       <c r="F12" s="7">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="H12" s="9">
-        <v>900000</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="9">
+        <f>E12*IF(F12&gt;0,F12,1)*IF(H12&gt;0,H12,1)*IF(J12&gt;0,J12,1)</f>
+        <v>171000</v>
+      </c>
+      <c r="M12" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B13" s="7">
         <v>4</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E13" s="9">
-        <v>35000</v>
+        <v>18000</v>
       </c>
       <c r="F13" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H13" s="9">
-        <v>700000</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="9">
+        <f>E13*IF(F13&gt;0,F13,1)*IF(H13&gt;0,H13,1)*IF(J13&gt;0,J13,1)</f>
+        <v>432000</v>
+      </c>
+      <c r="M13" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C14" s="10"/>
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
       <c r="F14" s="10"/>
       <c r="G14" s="10"/>
-      <c r="H14" s="11">
-        <f>SUM(H10:H13)</f>
-        <v>2750000</v>
-      </c>
-      <c r="I14" s="12"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="11">
+        <f>SUM(L10:L13)</f>
+        <v>3420600</v>
+      </c>
+      <c r="M14" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="B3:M3"/>
+    <mergeCell ref="B14:K14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/samples/Template_Pengajuan_Resmi_Yayasan.xlsx
+++ b/samples/Template_Pengajuan_Resmi_Yayasan.xlsx
@@ -11,127 +11,304 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="96">
   <si>
     <t>YAYASAN PENDIDIKAN ISLAM PONDOK PESANTREN AL-QUR'ANIYYAH</t>
   </si>
   <si>
-    <t>FORMAT STANDAR PENGAJUAN ANGGARAN BELANJA UNIT (TA 2026)</t>
+    <t>FORMAT USULAN RENCANA ANGGARAN BELANJA (RAB) UNIT</t>
   </si>
   <si>
     <t>Unit Pemohon:</t>
   </si>
   <si>
-    <t>SMP IT Al-Qur'aniyyah</t>
+    <t>SMA IT Al-Qur'aniyyah</t>
   </si>
   <si>
     <t>Nama Kegiatan:</t>
   </si>
   <si>
-    <t>STS Semester Ganjil / Kegiatan Tahunan</t>
+    <t>Ujian Satuan Pendidikan &amp; TKA</t>
   </si>
   <si>
     <t>Tahun Anggaran:</t>
   </si>
   <si>
-    <t>2026</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Kategori</t>
-  </si>
-  <si>
-    <t>Uraian Barang / Belanja Kegiatan</t>
-  </si>
-  <si>
-    <t>Harga Satuan</t>
-  </si>
-  <si>
-    <t>Volume 1</t>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>URAIAN KEGIATAN</t>
+  </si>
+  <si>
+    <t>BIAYA</t>
+  </si>
+  <si>
+    <t>RINCIAN</t>
+  </si>
+  <si>
+    <t>JUMLAH</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Vol 1</t>
   </si>
   <si>
     <t>Satuan 1</t>
   </si>
   <si>
-    <t>Volume 2</t>
+    <t>x</t>
+  </si>
+  <si>
+    <t>Vol 2</t>
   </si>
   <si>
     <t>Satuan 2</t>
   </si>
   <si>
-    <t>Volume 3</t>
+    <t>Vol 3</t>
   </si>
   <si>
     <t>Satuan 3</t>
   </si>
   <si>
-    <t>Jumlah</t>
-  </si>
-  <si>
-    <t>Keterangan</t>
-  </si>
-  <si>
-    <t>ATK</t>
-  </si>
-  <si>
-    <t>Penggandaan LJK (Lembar Jawaban Komputer)</t>
-  </si>
-  <si>
-    <t>MP</t>
-  </si>
-  <si>
-    <t>Siswa</t>
-  </si>
-  <si>
-    <t>Lembar</t>
-  </si>
-  <si>
-    <t>16 MP × 237 Siswa × 2 Lembar</t>
-  </si>
-  <si>
-    <t>Upah</t>
-  </si>
-  <si>
-    <t>Pembuatan Soal Ujian</t>
-  </si>
-  <si>
-    <t>Kelas</t>
-  </si>
-  <si>
-    <t>16 MP × 3 Kelas</t>
-  </si>
-  <si>
-    <t>Kertas HVS F4 70 gram</t>
-  </si>
-  <si>
-    <t>Rim</t>
-  </si>
-  <si>
-    <t>Kebutuhan cetak ujian</t>
-  </si>
-  <si>
-    <t>Konsumsi</t>
-  </si>
-  <si>
-    <t>Snack Rapat Koordinasi Panitia</t>
-  </si>
-  <si>
-    <t>Kotak</t>
-  </si>
-  <si>
-    <t>Persiapan panitia</t>
-  </si>
-  <si>
-    <t>TOTAL USULAN ANGGARAN</t>
+    <t>I</t>
+  </si>
+  <si>
+    <t>ANGGARAN DANA TKA</t>
+  </si>
+  <si>
+    <t>1.</t>
+  </si>
+  <si>
+    <t>Pengadaan modul/panduan/foto copy (102 siswa + 9 guru + arsip 1)</t>
+  </si>
+  <si>
+    <t>buah</t>
+  </si>
+  <si>
+    <t>paket</t>
+  </si>
+  <si>
+    <t>2.</t>
+  </si>
+  <si>
+    <t>Insentif &amp; transport guru pembina PM</t>
+  </si>
+  <si>
+    <t>mapel</t>
+  </si>
+  <si>
+    <t>pertemuan</t>
+  </si>
+  <si>
+    <t>bulan</t>
+  </si>
+  <si>
+    <t>3.</t>
+  </si>
+  <si>
+    <t>Insentif panitia (Kepsek, Wakil, TU, Proktor, Operator, 3 Walas, OB)</t>
+  </si>
+  <si>
+    <t>orang</t>
+  </si>
+  <si>
+    <t>kegiatan</t>
+  </si>
+  <si>
+    <t>hari</t>
+  </si>
+  <si>
+    <t>4.</t>
+  </si>
+  <si>
+    <t>Konsumsi Pelaksanaan TKA</t>
+  </si>
+  <si>
+    <t>org</t>
+  </si>
+  <si>
+    <t>5.</t>
+  </si>
+  <si>
+    <t>Honor Pengawas Silang</t>
+  </si>
+  <si>
+    <t>sesi</t>
+  </si>
+  <si>
+    <t>6.</t>
+  </si>
+  <si>
+    <t>Transport Pengawas Silang</t>
+  </si>
+  <si>
+    <t>7.</t>
+  </si>
+  <si>
+    <t>Transport Monitoring Dinas</t>
+  </si>
+  <si>
+    <t>Org</t>
+  </si>
+  <si>
+    <t>8.</t>
+  </si>
+  <si>
+    <t>Konsumsi Monitoring Dinas</t>
+  </si>
+  <si>
+    <t>II</t>
+  </si>
+  <si>
+    <t>PELAKSANAAN UJIAN SATUAN PENDIDIKAN</t>
+  </si>
+  <si>
+    <t>Insentif ujian praktik</t>
+  </si>
+  <si>
+    <t>siswa</t>
+  </si>
+  <si>
+    <t>penyusunan kartu soal ujian dan kisi-kisi</t>
+  </si>
+  <si>
+    <t>Penyusunan naskah dan pengetikan soal (Ujian Tulis)</t>
+  </si>
+  <si>
+    <t>Penggandaan soal</t>
+  </si>
+  <si>
+    <t>lembar</t>
+  </si>
+  <si>
+    <t>Insentif pengawas ruang USP</t>
+  </si>
+  <si>
+    <t>ruang</t>
+  </si>
+  <si>
+    <t>Insentif korektor soal USP</t>
+  </si>
+  <si>
+    <t>korektor</t>
+  </si>
+  <si>
+    <t>Transport korektor soal USP</t>
+  </si>
+  <si>
+    <t>Transport monitoring Dinas</t>
+  </si>
+  <si>
+    <t>9.</t>
+  </si>
+  <si>
+    <t>Transport rapat panitia, pengawas, dan guru</t>
+  </si>
+  <si>
+    <t>10.</t>
+  </si>
+  <si>
+    <t>Insentif panitia US (Ketua, 3 walas, 2 wakasek, Sekretaris, Bendahara, TU, OB)</t>
+  </si>
+  <si>
+    <t>11. a).</t>
+  </si>
+  <si>
+    <t>Konsumsi: Saat ujian (Pengawas 8 orang dan panitia 6 orang)</t>
+  </si>
+  <si>
+    <t>11. b).</t>
+  </si>
+  <si>
+    <t>Konsumsi: Koreksi ujian</t>
+  </si>
+  <si>
+    <t>11. c).</t>
+  </si>
+  <si>
+    <t>Konsumsi: Konsumsi rapat</t>
+  </si>
+  <si>
+    <t>11. d).</t>
+  </si>
+  <si>
+    <t>Konsumsi: konsumsi rapat kelulusan</t>
+  </si>
+  <si>
+    <t>guru</t>
+  </si>
+  <si>
+    <t>III</t>
+  </si>
+  <si>
+    <t>KESEKRETARIATAN</t>
+  </si>
+  <si>
+    <t>Pembuatan lebel/kartu (siswa 102)</t>
+  </si>
+  <si>
+    <t>Pembelian plastik lebel</t>
+  </si>
+  <si>
+    <t>Penyusunan program dan laporan</t>
+  </si>
+  <si>
+    <t>bundel</t>
+  </si>
+  <si>
+    <t>Pembuatan spanduk</t>
+  </si>
+  <si>
+    <t>Cetak blanko Ijazah</t>
+  </si>
+  <si>
+    <t>Tanda tangan Ijazah</t>
+  </si>
+  <si>
+    <t>Pas Foto</t>
+  </si>
+  <si>
+    <t>Pembelian 1 set perlengkapan USP</t>
+  </si>
+  <si>
+    <t>sampul/map transparan untuk ijazah</t>
+  </si>
+  <si>
+    <t>Penandatanganan USP 1 ( Pengawas )</t>
+  </si>
+  <si>
+    <t>11.</t>
+  </si>
+  <si>
+    <t>Amplop Soal, lem, steples, map, lebel dll (ATK)</t>
+  </si>
+  <si>
+    <t>IV</t>
+  </si>
+  <si>
+    <t>PENGELOLAAN DATA, NILAI RAPORT KE PERGURUAN TINGGI</t>
+  </si>
+  <si>
+    <t>Pengumpulan berkas dan data siswa (print out, foto copy &amp; jilid)</t>
+  </si>
+  <si>
+    <t>pengolahan dan penginputan data &amp; nilai ke PDSS (oleh Walas &amp; Ops)</t>
+  </si>
+  <si>
+    <t>TOTAL USULAN KESELURUHAN</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="8" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;Rp &quot;#,##0"/>
+  </numFmts>
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -141,27 +318,36 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF1B4332"/>
-      <sz val="14"/>
+      <color rgb="FF1E3A8A"/>
+      <sz val="13"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF2D6A4F"/>
+      <color rgb="FF374151"/>
       <sz val="11"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="10"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
+      <color rgb="FF111827"/>
+      <sz val="9"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="9"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -171,12 +357,12 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF1B4332"/>
+      <color rgb="FF1E3A8A"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -185,16 +371,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1B4332"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0F4F0"/>
+        <fgColor rgb="FFF3F4F6"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -204,42 +385,61 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFD0D0D0"/>
+        <color rgb="FF9CA3AF"/>
       </left>
       <right style="thin">
-        <color rgb="FFD0D0D0"/>
+        <color rgb="FF9CA3AF"/>
       </right>
       <top style="thin">
-        <color rgb="FFD0D0D0"/>
+        <color rgb="FF9CA3AF"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFD0D0D0"/>
+        <color rgb="FF9CA3AF"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFE0E0E0"/>
+        <color rgb="FFD1D5DB"/>
       </left>
       <right style="thin">
-        <color rgb="FFE0E0E0"/>
+        <color rgb="FFD1D5DB"/>
       </right>
       <top style="thin">
-        <color rgb="FFE0E0E0"/>
+        <color rgb="FF9CA3AF"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFE0E0E0"/>
+        <color rgb="FF9CA3AF"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FFD1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top style="hair">
+        <color rgb="FFE5E7EB"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="FFE5E7EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9CA3AF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9CA3AF"/>
+      </right>
       <top style="medium">
-        <color rgb="FF1B4332"/>
+        <color rgb="FF1F2937"/>
       </top>
       <bottom style="double">
-        <color rgb="FF1B4332"/>
+        <color rgb="FF1F2937"/>
       </bottom>
       <diagonal/>
     </border>
@@ -247,7 +447,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -256,31 +456,32 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -620,28 +821,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:M14"/>
-  <sheetFormatPr defaultRowHeight="22" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:M50"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="6" customWidth="1"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="44" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="38" customWidth="1"/>
-    <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="4" customWidth="1"/>
+    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="4" customWidth="1"/>
+    <col min="10" max="10" width="8" customWidth="1"/>
     <col min="11" max="11" width="12" customWidth="1"/>
-    <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="30" customWidth="1"/>
+    <col min="12" max="13" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -654,10 +858,11 @@
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="2" t="s">
-        <v>1</v>
-      </c>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -674,7 +879,7 @@
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="4" t="s">
         <v>3</v>
       </c>
     </row>
@@ -682,7 +887,7 @@
       <c r="B6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="4" t="s">
         <v>5</v>
       </c>
     </row>
@@ -690,210 +895,1363 @@
       <c r="B7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" ht="26" customHeight="1" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="M9" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="4" t="s">
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="E10" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="I9" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J9" s="4" t="s">
+      <c r="F10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="H10" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="L9" s="6" t="s">
+      <c r="I10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J10" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="M9" s="4" t="s">
+      <c r="K10" s="5" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="10" ht="22" customHeight="1" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B10" s="7">
-        <v>1</v>
-      </c>
-      <c r="C10" s="8" t="s">
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="9">
-        <v>150</v>
-      </c>
-      <c r="F10" s="7">
-        <v>16</v>
-      </c>
-      <c r="G10" s="7" t="s">
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="9">
+        <f>=SUM(L12:L19)</f>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="H10" s="7">
-        <v>237</v>
-      </c>
-      <c r="I10" s="7" t="s">
+      <c r="B12" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="J10" s="7">
+      <c r="C12" s="12">
+        <v>25000</v>
+      </c>
+      <c r="D12" s="10">
+        <v>102</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="10">
+        <v>5</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="12">
+        <f>=C12*D12*IF(G12&gt;0,G12,1)*IF(J12&gt;0,J12,1)</f>
+      </c>
+      <c r="M12" s="11"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="12">
+        <v>150000</v>
+      </c>
+      <c r="D13" s="10">
+        <v>9</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="10">
+        <v>8</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J13" s="10">
+        <v>1</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="L13" s="12">
+        <f>=C13*D13*IF(G13&gt;0,G13,1)*IF(J13&gt;0,J13,1)</f>
+      </c>
+      <c r="M13" s="11"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="12">
+        <v>75000</v>
+      </c>
+      <c r="D14" s="10">
+        <v>10</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="10">
+        <v>1</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J14" s="10">
+        <v>13</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="L14" s="12">
+        <f>=C14*D14*IF(G14&gt;0,G14,1)*IF(J14&gt;0,J14,1)</f>
+      </c>
+      <c r="M14" s="11"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="12">
+        <v>50000</v>
+      </c>
+      <c r="D15" s="10">
+        <v>4</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="10">
+        <v>12</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="12">
+        <f>=C15*D15*IF(G15&gt;0,G15,1)*IF(J15&gt;0,J15,1)</f>
+      </c>
+      <c r="M15" s="11"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="12">
+        <v>50000</v>
+      </c>
+      <c r="D16" s="10">
+        <v>4</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="10">
         <v>2</v>
       </c>
-      <c r="K10" s="7" t="s">
+      <c r="H16" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J16" s="10">
+        <v>3</v>
+      </c>
+      <c r="K16" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="L16" s="12">
+        <f>=C16*D16*IF(G16&gt;0,G16,1)*IF(J16&gt;0,J16,1)</f>
+      </c>
+      <c r="M16" s="11"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="12">
+        <v>50000</v>
+      </c>
+      <c r="D17" s="10">
+        <v>4</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="10">
+        <v>2</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="12">
+        <f>=C17*D17*IF(G17&gt;0,G17,1)*IF(J17&gt;0,J17,1)</f>
+      </c>
+      <c r="M17" s="11"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="12">
+        <v>500000</v>
+      </c>
+      <c r="D18" s="10">
+        <v>3</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" s="10">
+        <v>1</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="12">
+        <f>=C18*D18*IF(G18&gt;0,G18,1)*IF(J18&gt;0,J18,1)</f>
+      </c>
+      <c r="M18" s="11"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="12">
+        <v>100000</v>
+      </c>
+      <c r="D19" s="10">
+        <v>3</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="12">
+        <f>=C19*D19*IF(G19&gt;0,G19,1)*IF(J19&gt;0,J19,1)</f>
+      </c>
+      <c r="M19" s="11"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="9">
+        <f>=SUM(L21:L34)</f>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="12">
+        <v>10000</v>
+      </c>
+      <c r="D21" s="10">
+        <v>13</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21" s="10">
+        <v>102</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="12">
+        <f>=C21*D21*IF(G21&gt;0,G21,1)*IF(J21&gt;0,J21,1)</f>
+      </c>
+      <c r="M21" s="11"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="12">
+        <v>75000</v>
+      </c>
+      <c r="D22" s="10">
+        <v>17</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" s="10">
+        <v>2</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="12">
+        <f>=C22*D22*IF(G22&gt;0,G22,1)*IF(J22&gt;0,J22,1)</f>
+      </c>
+      <c r="M22" s="11"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="12">
+        <v>35000</v>
+      </c>
+      <c r="D23" s="10">
+        <v>17</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G23" s="10">
+        <v>2</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="12">
+        <f>=C23*D23*IF(G23&gt;0,G23,1)*IF(J23&gt;0,J23,1)</f>
+      </c>
+      <c r="M23" s="11"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24" s="12">
+        <v>200</v>
+      </c>
+      <c r="D24" s="10">
+        <v>17</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G24" s="10">
+        <v>10</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J24" s="10">
+        <v>102</v>
+      </c>
+      <c r="K24" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="L24" s="12">
+        <f>=C24*D24*IF(G24&gt;0,G24,1)*IF(J24&gt;0,J24,1)</f>
+      </c>
+      <c r="M24" s="11"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C25" s="12">
+        <v>30000</v>
+      </c>
+      <c r="D25" s="10">
+        <v>17</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" s="10">
+        <v>4</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J25" s="10">
+        <v>2</v>
+      </c>
+      <c r="K25" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="L25" s="12">
+        <f>=C25*D25*IF(G25&gt;0,G25,1)*IF(J25&gt;0,J25,1)</f>
+      </c>
+      <c r="M25" s="11"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26" s="12">
+        <v>5000</v>
+      </c>
+      <c r="D26" s="10">
+        <v>17</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G26" s="10">
+        <v>102</v>
+      </c>
+      <c r="H26" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J26" s="10">
+        <v>2</v>
+      </c>
+      <c r="K26" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="L26" s="12">
+        <f>=C26*D26*IF(G26&gt;0,G26,1)*IF(J26&gt;0,J26,1)</f>
+      </c>
+      <c r="M26" s="11"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C27" s="12">
+        <v>50000</v>
+      </c>
+      <c r="D27" s="10">
+        <v>17</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G27" s="10">
+        <v>2</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="12">
+        <f>=C27*D27*IF(G27&gt;0,G27,1)*IF(J27&gt;0,J27,1)</f>
+      </c>
+      <c r="M27" s="11"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C28" s="12">
+        <v>500000</v>
+      </c>
+      <c r="D28" s="10">
+        <v>3</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28" s="10">
+        <v>1</v>
+      </c>
+      <c r="H28" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="12">
+        <f>=C28*D28*IF(G28&gt;0,G28,1)*IF(J28&gt;0,J28,1)</f>
+      </c>
+      <c r="M28" s="11"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C29" s="12">
+        <v>50000</v>
+      </c>
+      <c r="D29" s="10">
+        <v>27</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G29" s="10">
+        <v>1</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="I29" s="10"/>
+      <c r="J29" s="10"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="12">
+        <f>=C29*D29*IF(G29&gt;0,G29,1)*IF(J29&gt;0,J29,1)</f>
+      </c>
+      <c r="M29" s="11"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30" s="12">
+        <v>75000</v>
+      </c>
+      <c r="D30" s="10">
+        <v>9</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G30" s="10">
+        <v>1</v>
+      </c>
+      <c r="H30" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I30" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J30" s="10">
+        <v>8</v>
+      </c>
+      <c r="K30" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="L30" s="12">
+        <f>=C30*D30*IF(G30&gt;0,G30,1)*IF(J30&gt;0,J30,1)</f>
+      </c>
+      <c r="M30" s="11"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C31" s="12">
+        <v>10000</v>
+      </c>
+      <c r="D31" s="10">
+        <v>14</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G31" s="10">
+        <v>12</v>
+      </c>
+      <c r="H31" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="I31" s="10"/>
+      <c r="J31" s="10"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="12">
+        <f>=C31*D31*IF(G31&gt;0,G31,1)*IF(J31&gt;0,J31,1)</f>
+      </c>
+      <c r="M31" s="11"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C32" s="12">
+        <v>30000</v>
+      </c>
+      <c r="D32" s="10">
+        <v>27</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G32" s="10">
+        <v>1</v>
+      </c>
+      <c r="H32" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I32" s="10"/>
+      <c r="J32" s="10"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="12">
+        <f>=C32*D32*IF(G32&gt;0,G32,1)*IF(J32&gt;0,J32,1)</f>
+      </c>
+      <c r="M32" s="11"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C33" s="12">
+        <v>30000</v>
+      </c>
+      <c r="D33" s="10">
+        <v>27</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G33" s="10">
+        <v>1</v>
+      </c>
+      <c r="H33" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="I33" s="10"/>
+      <c r="J33" s="10"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="12">
+        <f>=C33*D33*IF(G33&gt;0,G33,1)*IF(J33&gt;0,J33,1)</f>
+      </c>
+      <c r="M33" s="11"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C34" s="12">
+        <v>30000</v>
+      </c>
+      <c r="D34" s="10">
+        <v>27</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G34" s="10">
+        <v>1</v>
+      </c>
+      <c r="H34" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I34" s="10"/>
+      <c r="J34" s="10"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="12">
+        <f>=C34*D34*IF(G34&gt;0,G34,1)*IF(J34&gt;0,J34,1)</f>
+      </c>
+      <c r="M34" s="11"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="8"/>
+      <c r="K35" s="8"/>
+      <c r="L35" s="8"/>
+      <c r="M35" s="9">
+        <f>=SUM(L36:L46)</f>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C36" s="12">
+        <v>2000</v>
+      </c>
+      <c r="D36" s="10">
+        <v>102</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F36" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G36" s="10">
+        <v>1</v>
+      </c>
+      <c r="H36" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I36" s="10"/>
+      <c r="J36" s="10"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="12">
+        <f>=C36*D36*IF(G36&gt;0,G36,1)*IF(J36&gt;0,J36,1)</f>
+      </c>
+      <c r="M36" s="11"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C37" s="12">
+        <v>2000</v>
+      </c>
+      <c r="D37" s="10">
+        <v>102</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G37" s="10">
+        <v>1</v>
+      </c>
+      <c r="H37" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I37" s="10"/>
+      <c r="J37" s="10"/>
+      <c r="K37" s="11"/>
+      <c r="L37" s="12">
+        <f>=C37*D37*IF(G37&gt;0,G37,1)*IF(J37&gt;0,J37,1)</f>
+      </c>
+      <c r="M37" s="11"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C38" s="12">
+        <v>75000</v>
+      </c>
+      <c r="D38" s="10">
+        <v>2</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G38" s="10">
+        <v>1</v>
+      </c>
+      <c r="H38" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I38" s="10"/>
+      <c r="J38" s="10"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="12">
+        <f>=C38*D38*IF(G38&gt;0,G38,1)*IF(J38&gt;0,J38,1)</f>
+      </c>
+      <c r="M38" s="11"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="C39" s="12">
+        <v>150000</v>
+      </c>
+      <c r="D39" s="10">
+        <v>1</v>
+      </c>
+      <c r="E39" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="L10" s="9">
-        <f>E10*IF(F10&gt;0,F10,1)*IF(H10&gt;0,H10,1)*IF(J10&gt;0,J10,1)</f>
-        <v>1137600</v>
-      </c>
-      <c r="M10" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B11" s="7">
-        <v>2</v>
-      </c>
-      <c r="C11" s="8" t="s">
+      <c r="F39" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G39" s="10">
+        <v>1</v>
+      </c>
+      <c r="H39" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I39" s="10"/>
+      <c r="J39" s="10"/>
+      <c r="K39" s="11"/>
+      <c r="L39" s="12">
+        <f>=C39*D39*IF(G39&gt;0,G39,1)*IF(J39&gt;0,J39,1)</f>
+      </c>
+      <c r="M39" s="11"/>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C40" s="12">
+        <v>10000</v>
+      </c>
+      <c r="D40" s="10">
+        <v>102</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F40" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G40" s="10">
+        <v>1</v>
+      </c>
+      <c r="H40" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I40" s="10"/>
+      <c r="J40" s="10"/>
+      <c r="K40" s="11"/>
+      <c r="L40" s="12">
+        <f>=C40*D40*IF(G40&gt;0,G40,1)*IF(J40&gt;0,J40,1)</f>
+      </c>
+      <c r="M40" s="11"/>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="C41" s="12">
+        <v>25000</v>
+      </c>
+      <c r="D41" s="10">
+        <v>102</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G41" s="10">
+        <v>1</v>
+      </c>
+      <c r="H41" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I41" s="10"/>
+      <c r="J41" s="10"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="12">
+        <f>=C41*D41*IF(G41&gt;0,G41,1)*IF(J41&gt;0,J41,1)</f>
+      </c>
+      <c r="M41" s="11"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="C42" s="12">
+        <v>30000</v>
+      </c>
+      <c r="D42" s="10">
+        <v>102</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F42" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G42" s="10">
+        <v>1</v>
+      </c>
+      <c r="H42" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I42" s="10"/>
+      <c r="J42" s="10"/>
+      <c r="K42" s="11"/>
+      <c r="L42" s="12">
+        <f>=C42*D42*IF(G42&gt;0,G42,1)*IF(J42&gt;0,J42,1)</f>
+      </c>
+      <c r="M42" s="11"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C43" s="12">
+        <v>25000</v>
+      </c>
+      <c r="D43" s="10">
+        <v>102</v>
+      </c>
+      <c r="E43" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G43" s="10">
+        <v>1</v>
+      </c>
+      <c r="H43" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="11"/>
+      <c r="L43" s="12">
+        <f>=C43*D43*IF(G43&gt;0,G43,1)*IF(J43&gt;0,J43,1)</f>
+      </c>
+      <c r="M43" s="11"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C44" s="12">
+        <v>3000</v>
+      </c>
+      <c r="D44" s="10">
+        <v>102</v>
+      </c>
+      <c r="E44" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F44" s="10"/>
+      <c r="G44" s="10"/>
+      <c r="H44" s="11"/>
+      <c r="I44" s="10"/>
+      <c r="J44" s="10"/>
+      <c r="K44" s="11"/>
+      <c r="L44" s="12">
+        <f>=C44*D44*IF(G44&gt;0,G44,1)*IF(J44&gt;0,J44,1)</f>
+      </c>
+      <c r="M44" s="11"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B45" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C45" s="12">
+        <v>500000</v>
+      </c>
+      <c r="D45" s="10">
+        <v>1</v>
+      </c>
+      <c r="E45" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G45" s="10">
+        <v>1</v>
+      </c>
+      <c r="H45" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I45" s="10"/>
+      <c r="J45" s="10"/>
+      <c r="K45" s="11"/>
+      <c r="L45" s="12">
+        <f>=C45*D45*IF(G45&gt;0,G45,1)*IF(J45&gt;0,J45,1)</f>
+      </c>
+      <c r="M45" s="11"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C46" s="12">
+        <v>60000</v>
+      </c>
+      <c r="D46" s="10">
+        <v>1</v>
+      </c>
+      <c r="E46" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F46" s="10"/>
+      <c r="G46" s="10"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="10"/>
+      <c r="J46" s="10"/>
+      <c r="K46" s="11"/>
+      <c r="L46" s="12">
+        <f>=C46*D46*IF(G46&gt;0,G46,1)*IF(J46&gt;0,J46,1)</f>
+      </c>
+      <c r="M46" s="11"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="8"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="8"/>
+      <c r="I47" s="8"/>
+      <c r="J47" s="8"/>
+      <c r="K47" s="8"/>
+      <c r="L47" s="8"/>
+      <c r="M47" s="9">
+        <f>=SUM(L48:L49)</f>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C48" s="12">
+        <v>5000</v>
+      </c>
+      <c r="D48" s="10">
+        <v>102</v>
+      </c>
+      <c r="E48" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F48" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G48" s="10">
+        <v>1</v>
+      </c>
+      <c r="H48" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I48" s="10"/>
+      <c r="J48" s="10"/>
+      <c r="K48" s="11"/>
+      <c r="L48" s="12">
+        <f>=C48*D48*IF(G48&gt;0,G48,1)*IF(J48&gt;0,J48,1)</f>
+      </c>
+      <c r="M48" s="11"/>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" s="9">
-        <v>35000</v>
-      </c>
-      <c r="F11" s="7">
-        <v>16</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="H11" s="7">
-        <v>3</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="9">
-        <f>E11*IF(F11&gt;0,F11,1)*IF(H11&gt;0,H11,1)*IF(J11&gt;0,J11,1)</f>
-        <v>1680000</v>
-      </c>
-      <c r="M11" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B12" s="7">
-        <v>3</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E12" s="9">
-        <v>57000</v>
-      </c>
-      <c r="F12" s="7">
-        <v>3</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="9">
-        <f>E12*IF(F12&gt;0,F12,1)*IF(H12&gt;0,H12,1)*IF(J12&gt;0,J12,1)</f>
-        <v>171000</v>
-      </c>
-      <c r="M12" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B13" s="7">
-        <v>4</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="8" t="s">
+      <c r="B49" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="C49" s="12">
+        <v>30000</v>
+      </c>
+      <c r="D49" s="10">
+        <v>102</v>
+      </c>
+      <c r="E49" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F49" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G49" s="10">
+        <v>1</v>
+      </c>
+      <c r="H49" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E13" s="9">
-        <v>18000</v>
-      </c>
-      <c r="F13" s="7">
-        <v>24</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="9">
-        <f>E13*IF(F13&gt;0,F13,1)*IF(H13&gt;0,H13,1)*IF(J13&gt;0,J13,1)</f>
-        <v>432000</v>
-      </c>
-      <c r="M13" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B14" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="11">
-        <f>SUM(L10:L13)</f>
-        <v>3420600</v>
-      </c>
-      <c r="M14" s="12"/>
+      <c r="I49" s="10"/>
+      <c r="J49" s="10"/>
+      <c r="K49" s="11"/>
+      <c r="L49" s="12">
+        <f>=C49*D49*IF(G49&gt;0,G49,1)*IF(J49&gt;0,J49,1)</f>
+      </c>
+      <c r="M49" s="11"/>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="B50" s="13"/>
+      <c r="C50" s="13"/>
+      <c r="D50" s="13"/>
+      <c r="E50" s="13"/>
+      <c r="F50" s="13"/>
+      <c r="G50" s="13"/>
+      <c r="H50" s="13"/>
+      <c r="I50" s="13"/>
+      <c r="J50" s="13"/>
+      <c r="K50" s="13"/>
+      <c r="L50" s="14">
+        <f>=M11+M20+M35+M47</f>
+      </c>
+      <c r="M50" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="B3:M3"/>
-    <mergeCell ref="B14:K14"/>
+  <mergeCells count="9">
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="D9:K9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="M9:M10"/>
+    <mergeCell ref="A50:K50"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>